--- a/NOVEMBER/NOVEMBER KITCHEN OUTSTANDING/NOVEMBER RAFI SEAFOOD OUTSTANDING.xlsx
+++ b/NOVEMBER/NOVEMBER KITCHEN OUTSTANDING/NOVEMBER RAFI SEAFOOD OUTSTANDING.xlsx
@@ -27,276 +27,7 @@
 </file>
 
 <file path=xl/cellimages.xml><?xml version="1.0" encoding="utf-8"?>
-<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="ID_7BF01879F5304626B866F9D1EC0B9718" descr="WhatsApp Image 2025-11-04 at 16.19.15_3b354860"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:srcRect t="9479" r="3302" b="22209"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6369685" y="3664585"/>
-          <a:ext cx="5462905" cy="6882130"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="ID_61A6B6D73D3A4854A82E473D394FEE5A"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:srcRect l="5918" t="9141" r="2874"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6718935" y="626110"/>
-          <a:ext cx="2601595" cy="3133090"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="ID_1931EB1B8CC94F76A8E1ECCB232924DE" descr="WhatsApp Image 2025-11-07 at 14.10.37_ea7f58a2"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId3"/>
-        <a:srcRect l="1726" t="10725" b="17618"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6876415" y="6966585"/>
-          <a:ext cx="2694305" cy="3502025"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="ID_ED1EE2DFF883415D8D5E1866FC075DE1" descr="WhatsApp Image 2025-11-12 at 10.57.54_b550ed35"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId4"/>
-        <a:srcRect l="1933" t="15224" r="2836" b="16377"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6493510" y="10323830"/>
-          <a:ext cx="2930525" cy="3740150"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="ID_DD7C71329EF1420BB6A1F509D8242FB3"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId5"/>
-        <a:srcRect l="1652" t="11840" b="16682"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6553200" y="13399770"/>
-          <a:ext cx="2807970" cy="3634740"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="ID_5B5F1B4600184CE69D0AAC65BDEFB0F0" descr="WhatsApp Image 2025-11-18 at 13.20.06_edeeeb1a"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId6"/>
-        <a:srcRect t="12595" b="13531"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7011670" y="16490315"/>
-          <a:ext cx="2823845" cy="3741420"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="22" name="ID_C9ED45B96FB44D8A8EA9EB8F2BDEF5E7" descr="WhatsApp Image 2025-11-25 at 10.51.34_e064b241"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId7"/>
-        <a:srcRect l="2884" t="13629" r="1639" b="17725"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7418070" y="23263860"/>
-          <a:ext cx="2573020" cy="3328670"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="27" name="ID_A0F30E7669374D90B0122D8131BA4785" descr="WhatsApp Image 2025-11-26 at 15.19.49_04c8c115"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId8"/>
-        <a:srcRect t="16915" r="1874" b="12833"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7209155" y="22679025"/>
-          <a:ext cx="2691765" cy="3419475"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="28" name="ID_178B981EF0C2474B958D59670E886CC4" descr="WhatsApp Image 2025-11-26 at 15.20.10_d2685970"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId9"/>
-        <a:srcRect l="3120" t="12733" r="2840" b="18923"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7115175" y="26256615"/>
-          <a:ext cx="3109595" cy="4029075"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="19" name="ID_1EE2C82CE44B458FA9F0899828E72E0F" descr="WhatsApp Image 2025-11-29 at 13.44.42_8bd71d87"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId10"/>
-        <a:srcRect t="11498" b="15696"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7374890" y="29285565"/>
-          <a:ext cx="2652395" cy="3467100"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-</etc:cellImages>
+<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData"/>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1483,6 +1214,409 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>62865</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2445385</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>948055</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="ID_61A6B6D73D3A4854A82E473D394FEE5A"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:srcRect l="5918" t="9141" r="2874"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6912610" y="418465"/>
+          <a:ext cx="2422525" cy="2917190"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>40640</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2426970</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>1505585</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="ID_7BF01879F5304626B866F9D1EC0B9718" descr="WhatsApp Image 2025-11-04 at 16.19.15_3b354860"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:srcRect t="9479" r="3302" b="22209"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6930390" y="3426460"/>
+          <a:ext cx="2386330" cy="3006725"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>27940</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2445385</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>615950</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="ID_1931EB1B8CC94F76A8E1ECCB232924DE" descr="WhatsApp Image 2025-11-07 at 14.10.37_ea7f58a2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:srcRect l="1726" t="10725" b="17618"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6912610" y="6479540"/>
+          <a:ext cx="2422525" cy="3148330"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>26035</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2441575</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>1560830</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="ID_C9ED45B96FB44D8A8EA9EB8F2BDEF5E7" descr="WhatsApp Image 2025-11-25 at 10.51.34_e064b241"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:srcRect l="2884" t="13629" r="1639" b="17725"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6915785" y="9674860"/>
+          <a:ext cx="2415540" cy="3125470"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>39370</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2445385</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>1543050</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="ID_ED1EE2DFF883415D8D5E1866FC075DE1" descr="WhatsApp Image 2025-11-12 at 10.57.54_b550ed35"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId5"/>
+        <a:srcRect l="1933" t="15224" r="2836" b="16377"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6912610" y="12866370"/>
+          <a:ext cx="2422525" cy="3091180"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2445385</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>1033780</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="ID_DD7C71329EF1420BB6A1F509D8242FB3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId6"/>
+        <a:srcRect l="1652" t="11840" b="16682"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6912610" y="16033750"/>
+          <a:ext cx="2422525" cy="3135630"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2442210</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>635000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="ID_5B5F1B4600184CE69D0AAC65BDEFB0F0" descr="WhatsApp Image 2025-11-18 at 13.20.06_edeeeb1a"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId7"/>
+        <a:srcRect t="12595" b="13531"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6915150" y="19225260"/>
+          <a:ext cx="2416810" cy="3202940"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>46990</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2445385</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>1536700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="27" name="ID_A0F30E7669374D90B0122D8131BA4785" descr="WhatsApp Image 2025-11-26 at 15.19.49_04c8c115"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId8"/>
+        <a:srcRect t="16915" r="1874" b="12833"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6912610" y="22487890"/>
+          <a:ext cx="2422525" cy="3077210"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>34290</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2445385</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>772795</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="28" name="ID_178B981EF0C2474B958D59670E886CC4" descr="WhatsApp Image 2025-11-26 at 15.20.10_d2685970"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId9"/>
+        <a:srcRect l="3120" t="12733" r="2840" b="18923"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6912610" y="25650190"/>
+          <a:ext cx="2422525" cy="3138805"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>27940</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2440305</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>1043305</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="ID_1EE2C82CE44B458FA9F0899828E72E0F" descr="WhatsApp Image 2025-11-29 at 13.44.42_8bd71d87"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId10"/>
+        <a:srcRect t="11498" b="15696"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6917690" y="28839160"/>
+          <a:ext cx="2412365" cy="3154045"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
@@ -1756,7 +1890,7 @@
     <col min="12" max="16384" width="9.14285714285714" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:7">
+    <row r="1" s="1" customFormat="1" ht="28" customHeight="1" spans="1:7">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1792,12 +1926,9 @@
       <c r="D2" s="8">
         <v>370000</v>
       </c>
-      <c r="E2" s="9" t="str">
-        <f>_xlfn.DISPIMG("ID_61A6B6D73D3A4854A82E473D394FEE5A",1)</f>
-        <v>=DISPIMG("ID_61A6B6D73D3A4854A82E473D394FEE5A",1)</v>
-      </c>
+      <c r="E2" s="9"/>
       <c r="F2" s="10">
-        <f t="shared" ref="F2:F9" si="0">SUM(C2*D2)</f>
+        <f t="shared" ref="F2:F8" si="0">SUM(C2*D2)</f>
         <v>1739000</v>
       </c>
       <c r="G2" s="11">
@@ -1854,10 +1985,7 @@
       <c r="D5" s="8">
         <v>180000</v>
       </c>
-      <c r="E5" s="9" t="str">
-        <f>_xlfn.DISPIMG("ID_7BF01879F5304626B866F9D1EC0B9718",1)</f>
-        <v>=DISPIMG("ID_7BF01879F5304626B866F9D1EC0B9718",1)</v>
-      </c>
+      <c r="E5" s="9"/>
       <c r="F5" s="10">
         <f t="shared" si="0"/>
         <v>540000</v>
@@ -1898,17 +2026,14 @@
       <c r="D7" s="8">
         <v>180000</v>
       </c>
-      <c r="E7" s="9" t="str">
-        <f>_xlfn.DISPIMG("ID_1931EB1B8CC94F76A8E1ECCB232924DE",1)</f>
-        <v>=DISPIMG("ID_1931EB1B8CC94F76A8E1ECCB232924DE",1)</v>
-      </c>
+      <c r="E7" s="9"/>
       <c r="F7" s="10">
         <f t="shared" si="0"/>
         <v>540000</v>
       </c>
       <c r="G7" s="11">
-        <f>SUM(C7*D7+C8*D8+C11*D11)</f>
-        <v>2382000</v>
+        <f>SUM(F7:F11)</f>
+        <v>3229000</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="50.4" customHeight="1" spans="1:7">
@@ -1941,7 +2066,9 @@
         <v>115000</v>
       </c>
       <c r="E9" s="13"/>
-      <c r="F9" s="10"/>
+      <c r="F9" s="10">
+        <v>218000</v>
+      </c>
       <c r="G9" s="14"/>
     </row>
     <row r="10" s="1" customFormat="1" ht="50.4" customHeight="1" spans="1:7">
@@ -1956,7 +2083,10 @@
         <v>370000</v>
       </c>
       <c r="E10" s="13"/>
-      <c r="F10" s="10"/>
+      <c r="F10" s="10">
+        <f t="shared" ref="F10:F13" si="1">SUM(C10*D10)</f>
+        <v>629000</v>
+      </c>
       <c r="G10" s="14"/>
     </row>
     <row r="11" s="1" customFormat="1" ht="50.4" customHeight="1" spans="1:7">
@@ -1972,7 +2102,7 @@
       </c>
       <c r="E11" s="19"/>
       <c r="F11" s="10">
-        <f t="shared" ref="F11:F13" si="1">SUM(C11*D11)</f>
+        <f t="shared" si="1"/>
         <v>1587000</v>
       </c>
       <c r="G11" s="20"/>
@@ -1990,10 +2120,7 @@
       <c r="D12" s="8">
         <v>180000</v>
       </c>
-      <c r="E12" s="23" t="str">
-        <f>_xlfn.DISPIMG("ID_C9ED45B96FB44D8A8EA9EB8F2BDEF5E7",1)</f>
-        <v>=DISPIMG("ID_C9ED45B96FB44D8A8EA9EB8F2BDEF5E7",1)</v>
-      </c>
+      <c r="E12" s="23"/>
       <c r="F12" s="10">
         <f t="shared" si="1"/>
         <v>360000</v>
@@ -2034,10 +2161,7 @@
       <c r="D14" s="26">
         <v>180000</v>
       </c>
-      <c r="E14" s="13" t="str">
-        <f>_xlfn.DISPIMG("ID_ED1EE2DFF883415D8D5E1866FC075DE1",1)</f>
-        <v>=DISPIMG("ID_ED1EE2DFF883415D8D5E1866FC075DE1",1)</v>
-      </c>
+      <c r="E14" s="13"/>
       <c r="F14" s="20">
         <f>C14*D14</f>
         <v>900000</v>
@@ -2078,12 +2202,9 @@
       <c r="D16" s="8">
         <v>370000</v>
       </c>
-      <c r="E16" s="9" t="str">
-        <f>_xlfn.DISPIMG("ID_DD7C71329EF1420BB6A1F509D8242FB3",1)</f>
-        <v>=DISPIMG("ID_DD7C71329EF1420BB6A1F509D8242FB3",1)</v>
-      </c>
+      <c r="E16" s="9"/>
       <c r="F16" s="10">
-        <f t="shared" ref="F16:F29" si="2">SUM(C16*D16)</f>
+        <f t="shared" ref="F16:F24" si="2">SUM(C16*D16)</f>
         <v>1406000</v>
       </c>
       <c r="G16" s="11">
@@ -2140,10 +2261,7 @@
       <c r="D19" s="8">
         <v>120000</v>
       </c>
-      <c r="E19" s="9" t="str">
-        <f>_xlfn.DISPIMG("ID_5B5F1B4600184CE69D0AAC65BDEFB0F0",1)</f>
-        <v>=DISPIMG("ID_5B5F1B4600184CE69D0AAC65BDEFB0F0",1)</v>
-      </c>
+      <c r="E19" s="9"/>
       <c r="F19" s="10">
         <f t="shared" si="2"/>
         <v>1752000</v>
@@ -2238,17 +2356,13 @@
       <c r="D24" s="8">
         <v>185000</v>
       </c>
-      <c r="E24" s="23" t="str">
-        <f>_xlfn.DISPIMG("ID_A0F30E7669374D90B0122D8131BA4785",1)</f>
-        <v>=DISPIMG("ID_A0F30E7669374D90B0122D8131BA4785",1)</v>
-      </c>
+      <c r="E24" s="23"/>
       <c r="F24" s="10">
         <f t="shared" si="2"/>
         <v>536500</v>
       </c>
       <c r="G24" s="10">
-        <f>SUM(C24*D24+C25*D25)</f>
-        <v>1551250</v>
+        <v>1919600</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="125" customHeight="1" spans="1:7">
@@ -2260,12 +2374,11 @@
         <v>3.69</v>
       </c>
       <c r="D25" s="8">
-        <v>275000</v>
+        <v>375000</v>
       </c>
       <c r="E25" s="23"/>
       <c r="F25" s="10">
-        <f t="shared" si="2"/>
-        <v>1014750</v>
+        <v>1383150</v>
       </c>
       <c r="G25" s="10"/>
     </row>
@@ -2282,12 +2395,9 @@
       <c r="D26" s="8">
         <v>120000</v>
       </c>
-      <c r="E26" s="9" t="str">
-        <f>_xlfn.DISPIMG("ID_178B981EF0C2474B958D59670E886CC4",1)</f>
-        <v>=DISPIMG("ID_178B981EF0C2474B958D59670E886CC4",1)</v>
-      </c>
+      <c r="E26" s="9"/>
       <c r="F26" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="F26:F29" si="3">SUM(C26*D26)</f>
         <v>948000</v>
       </c>
       <c r="G26" s="11">
@@ -2308,7 +2418,7 @@
       </c>
       <c r="E27" s="13"/>
       <c r="F27" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>414000</v>
       </c>
       <c r="G27" s="14"/>
@@ -2326,7 +2436,7 @@
       </c>
       <c r="E28" s="13"/>
       <c r="F28" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>225000</v>
       </c>
       <c r="G28" s="14"/>
@@ -2344,14 +2454,14 @@
       </c>
       <c r="E29" s="19"/>
       <c r="F29" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>351500</v>
       </c>
       <c r="G29" s="14"/>
     </row>
     <row r="30" s="1" customFormat="1" ht="84" customHeight="1" spans="1:7">
       <c r="A30" s="21">
-        <v>45963</v>
+        <v>45990</v>
       </c>
       <c r="B30" s="17" t="s">
         <v>16</v>
@@ -2362,12 +2472,9 @@
       <c r="D30" s="8">
         <v>370000</v>
       </c>
-      <c r="E30" s="9" t="str">
-        <f>_xlfn.DISPIMG("ID_1EE2C82CE44B458FA9F0899828E72E0F",1)</f>
-        <v>=DISPIMG("ID_1EE2C82CE44B458FA9F0899828E72E0F",1)</v>
-      </c>
+      <c r="E30" s="9"/>
       <c r="F30" s="10">
-        <f>C30*D30</f>
+        <f t="shared" ref="F30:F32" si="4">C30*D30</f>
         <v>1387500</v>
       </c>
       <c r="G30" s="11">
@@ -2388,7 +2495,7 @@
       </c>
       <c r="E31" s="13"/>
       <c r="F31" s="10">
-        <f>C31*D31</f>
+        <f t="shared" si="4"/>
         <v>269450</v>
       </c>
       <c r="G31" s="14"/>
@@ -2406,7 +2513,7 @@
       </c>
       <c r="E32" s="19"/>
       <c r="F32" s="10">
-        <f>C32*D32</f>
+        <f t="shared" si="4"/>
         <v>580900</v>
       </c>
       <c r="G32" s="20"/>
@@ -2417,7 +2524,7 @@
       <c r="C33" s="29"/>
       <c r="D33" s="30">
         <f>SUM(G2:G32)</f>
-        <v>20728100</v>
+        <v>21943450</v>
       </c>
       <c r="E33" s="30"/>
       <c r="F33" s="30"/>
@@ -2479,12 +2586,6 @@
     </row>
     <row r="52" s="1" customFormat="1" ht="42" customHeight="1" spans="1:8">
       <c r="A52" s="2"/>
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
-      <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
       <c r="H52" s="31"/>
     </row>
     <row r="53" s="1" customFormat="1" ht="125" customHeight="1" spans="1:1">
@@ -2513,12 +2614,6 @@
     </row>
     <row r="61" s="1" customFormat="1" ht="31" customHeight="1" spans="1:8">
       <c r="A61" s="2"/>
-      <c r="B61" s="1"/>
-      <c r="C61" s="1"/>
-      <c r="D61" s="1"/>
-      <c r="E61" s="1"/>
-      <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
       <c r="H61" s="31"/>
     </row>
   </sheetData>
@@ -2558,5 +2653,6 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>